--- a/sample-data/test-scenarios/test-5-incomplete/Valley_Express_Trucking_Driver_Roster.xlsx
+++ b/sample-data/test-scenarios/test-5-incomplete/Valley_Express_Trucking_Driver_Roster.xlsx
@@ -518,15 +518,11 @@
           <t>2020-01-15</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -574,15 +570,11 @@
           <t>2020-01-15</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -630,15 +622,11 @@
           <t>2020-01-15</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
